--- a/bin/rfr_agencies_source.xlsx
+++ b/bin/rfr_agencies_source.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa-github\bin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC65D15-1E0C-41B3-A875-DFBB3D44345E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703C272F-CC28-449B-9FE8-9495FB4FAD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Access Board</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>NEA</t>
+  </si>
+  <si>
+    <t>FY24</t>
   </si>
 </sst>
 </file>
@@ -550,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:W35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -571,7 +574,7 @@
     <col min="18" max="22" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -638,8 +641,11 @@
       <c r="V1" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -668,7 +674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -694,7 +700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -708,7 +714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -737,7 +743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -748,7 +754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -788,8 +794,11 @@
       <c r="V7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -833,7 +842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -841,7 +850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -861,23 +870,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -886,7 +895,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -897,7 +906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -945,6 +954,9 @@
       </c>
       <c r="V16" s="1">
         <v>0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">

--- a/bin/rfr_agencies_source.xlsx
+++ b/bin/rfr_agencies_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703C272F-CC28-449B-9FE8-9495FB4FAD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E536BE6F-30E4-4CE4-9A86-B3A15B5FFAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Access Board</t>
   </si>
@@ -205,6 +208,9 @@
   </si>
   <si>
     <t>FY24</t>
+  </si>
+  <si>
+    <t>FY25</t>
   </si>
 </sst>
 </file>
@@ -553,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -574,7 +580,7 @@
     <col min="18" max="22" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -644,8 +650,11 @@
       <c r="W1" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -674,7 +683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -700,7 +709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -714,7 +723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -743,7 +752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -754,7 +763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -798,7 +807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -842,7 +851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -850,7 +859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -870,23 +879,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -895,7 +904,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -906,7 +915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -957,6 +966,9 @@
       </c>
       <c r="W16" s="1">
         <v>1</v>
+      </c>
+      <c r="X16" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
